--- a/reports/20260507/UI_BLOCK_UNBLOCK_FEEDBACK_INT_PW.xlsx
+++ b/reports/20260507/UI_BLOCK_UNBLOCK_FEEDBACK_INT_PW.xlsx
@@ -537,14 +537,14 @@
       </c>
       <c r="N1" s="3" t="inlineStr">
         <is>
-          <t>67.98s</t>
+          <t>60.90s</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>12:16:12</t>
+          <t>12:55:33</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
@@ -566,7 +566,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>12:16:19</t>
+          <t>12:55:46</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -588,7 +588,7 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>12:16:19</t>
+          <t>12:55:46</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
@@ -610,7 +610,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>12:16:19</t>
+          <t>12:55:46</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -632,7 +632,7 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>12:16:19</t>
+          <t>12:55:46</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -654,7 +654,7 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>12:16:32</t>
+          <t>12:55:56</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -676,7 +676,7 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>12:16:32</t>
+          <t>12:55:56</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
@@ -698,7 +698,7 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>12:16:40</t>
+          <t>12:56:06</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -720,7 +720,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>12:16:41</t>
+          <t>12:56:07</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -742,7 +742,7 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>12:16:41</t>
+          <t>12:56:07</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -765,7 +765,7 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>12:16:41</t>
+          <t>12:56:07</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
@@ -787,7 +787,7 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>12:16:41</t>
+          <t>12:56:07</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -809,7 +809,7 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>12:16:48</t>
+          <t>12:56:09</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
@@ -831,7 +831,7 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>12:16:48</t>
+          <t>12:56:09</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -853,7 +853,7 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>12:16:50</t>
+          <t>12:56:10</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
@@ -876,7 +876,7 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>12:16:56</t>
+          <t>12:56:11</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
@@ -898,7 +898,7 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>12:16:57</t>
+          <t>12:56:12</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
@@ -920,7 +920,7 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>12:16:57</t>
+          <t>12:56:13</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
@@ -942,7 +942,7 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>12:17:02</t>
+          <t>12:56:20</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
@@ -964,7 +964,7 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>12:17:03</t>
+          <t>12:56:20</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
@@ -986,7 +986,7 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>12:17:04</t>
+          <t>12:56:22</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
@@ -1009,7 +1009,7 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>12:17:13</t>
+          <t>12:56:26</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
@@ -1031,7 +1031,7 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>12:17:18</t>
+          <t>12:56:32</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
